--- a/Support/Материалы.xlsx
+++ b/Support/Материалы.xlsx
@@ -2,17 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38610" windowHeight="17670" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Материалы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -27,6 +31,16 @@
       <name val="Carlito"/>
       <color rgb="FF1F2937"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,49 +57,41 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
+    <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -95,48 +101,40 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFECACA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF4B5563"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE5E7EB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF6B7280"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F4F6"/>
+          <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF1D4ED8"/>
+        <color rgb="FF166534"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFDBEAFE"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF065F46"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -154,6 +152,36 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF6B7280"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4B5563"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE5E7EB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF92400E"/>
       </font>
       <fill>
@@ -165,37 +193,16 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF065F46"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
         <color rgb="FF991B1B"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FFFECACA"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -268,9 +275,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaterialsTable" displayName="MaterialsTable" ref="A1:AO6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:AO6"/>
-  <tableColumns count="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaterialsTable" displayName="MaterialsTable" ref="A1:AN14" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:AN14"/>
+  <tableColumns count="40">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Категория"/>
     <tableColumn id="3" name="Подкатегория"/>
@@ -310,7 +317,6 @@
     <tableColumn id="37" name="Приоритет"/>
     <tableColumn id="38" name="Статус"/>
     <tableColumn id="39" name="Источник"/>
-    <tableColumn id="40" name="Дата проверки данных"/>
     <tableColumn id="41" name="Комментарий"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -505,6 +511,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -514,8 +522,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AN14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -529,18 +537,12 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="13" max="14"/>
+    <col width="19" customWidth="1" min="15" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="20" max="21"/>
+    <col width="17" customWidth="1" min="22" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -556,1288 +558,2867 @@
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="24" customWidth="1" min="38" max="38"/>
     <col width="44" customWidth="1" min="39" max="39"/>
-    <col width="19" customWidth="1" min="40" max="40"/>
-    <col width="34" customWidth="1" min="41" max="41"/>
+    <col width="34" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Подкатегория</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Производитель</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Материал / марка</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Химическая база</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Твёрдость</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Шкала твёрдости</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цвет</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Плотность</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Вязкость смеси</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Соотношение компонентов</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Время жизни смеси</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Время распалубки</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Полное отверждение</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Удлинение при разрыве</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Прочность при растяжении</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Сопротивление раздиру</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Усадка</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Мин. рабочая температура</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Макс. рабочая температура</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Стойкость к воде</t>
         </is>
       </c>
-      <c r="W1" s="5" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Стойкость к маслам</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Стойкость к топливу</t>
         </is>
       </c>
-      <c r="Y1" s="5" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Стойкость к УФ</t>
         </is>
       </c>
-      <c r="Z1" s="5" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Вакуумная дегазация</t>
         </is>
       </c>
-      <c r="AA1" s="5" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Пигментирование</t>
         </is>
       </c>
-      <c r="AB1" s="5" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Фасовка</t>
         </is>
       </c>
-      <c r="AC1" s="5" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="AD1" s="5" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Валюта</t>
         </is>
       </c>
-      <c r="AE1" s="5" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="AF1" s="5" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Дата проверки цены</t>
         </is>
       </c>
-      <c r="AG1" s="5" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Основное применение</t>
         </is>
       </c>
-      <c r="AH1" s="5" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Плюсы</t>
         </is>
       </c>
-      <c r="AI1" s="5" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ограничения / минусы</t>
         </is>
       </c>
-      <c r="AJ1" s="5" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Наши испытания</t>
         </is>
       </c>
-      <c r="AK1" s="5" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="AL1" s="5" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="AM1" s="5" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="AN1" s="5" t="inlineStr">
-        <is>
-          <t>Дата проверки данных</t>
-        </is>
-      </c>
-      <c r="AO1" s="5" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="68" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="2" ht="68.09999999999999" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PU-CAST-001</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Полиуретан</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Литьевой эластомер</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Polytek</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Poly 75-59</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="n">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Shore A</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="K2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>около 10 мин</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>около 16 ч</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="P2" s="9" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>588%</t>
         </is>
       </c>
-      <c r="Q2" s="9" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>637 psi</t>
         </is>
       </c>
-      <c r="R2" s="9" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>122 pli, Die C</t>
         </is>
       </c>
-      <c r="S2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="T2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="U2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="V2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="W2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="X2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Y2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Z2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AA2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AB2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AC2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AD2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AE2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AF2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AG2" s="9" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Мягкие защитные кожухи; демпферы; эластичные накладки</t>
         </is>
       </c>
-      <c r="AH2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AI2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AJ2" s="9" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>Не проводились</t>
         </is>
       </c>
-      <c r="AK2" s="12" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="AL2" s="12" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>Эталон / ориентир</t>
         </is>
       </c>
-      <c r="AM2" s="9" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>https://polytek.com/products/poly-75-59-liquid-rubber</t>
         </is>
       </c>
-      <c r="AN2" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AO2" s="9" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="68" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="68.09999999999999" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>PU-CAST-002</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Полиуретан</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Литьевой эластомер</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Polytek</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Poly 75-70</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="n">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Shore A</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>около 40 мин</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>около 16 ч</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="P3" s="9" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>724%</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>938 psi</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>299 pli, Die C</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="T3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="U3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="V3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="X3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Y3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Z3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AA3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AB3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AC3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AD3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AE3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AF3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AG3" s="9" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>Защитные кожухи; технические накладки; бамперы; гибкие корпуса</t>
         </is>
       </c>
-      <c r="AH3" s="9" t="inlineStr">
+      <c r="AH3" s="2" t="inlineStr">
         <is>
           <t>Рабочая эталонная точка около Shore A70; высокое заявленное удлинение и сопротивление раздиру</t>
         </is>
       </c>
-      <c r="AI3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AJ3" s="9" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>Не проводились</t>
         </is>
       </c>
-      <c r="AK3" s="12" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="AL3" s="12" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>Приоритетный кандидат</t>
         </is>
       </c>
-      <c r="AM3" s="9" t="inlineStr">
+      <c r="AM3" s="2" t="inlineStr">
         <is>
           <t>https://polytek.com/products/poly-75-70-liquid-rubber</t>
         </is>
       </c>
-      <c r="AN3" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AO3" s="9" t="inlineStr">
+      <c r="AN3" s="2" t="inlineStr">
         <is>
           <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="68.09999999999999" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PU-CAST-003</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Полиуретан</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Литьевой эластомер</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Polytek</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Poly 75-80</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Shore A</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>около 45 мин</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>около 16 ч</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>468%</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>750 psi</t>
         </is>
       </c>
-      <c r="R4" s="9" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>199 pli, Die C</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="X4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Y4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Z4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AA4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AB4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AC4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AD4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AE4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AF4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AG4" s="9" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
         <is>
           <t>Более жёсткие защитные кожухи; тонкостенные технические изделия</t>
         </is>
       </c>
-      <c r="AH4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AI4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AJ4" s="9" t="inlineStr">
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
         <is>
           <t>Не проводились</t>
         </is>
       </c>
-      <c r="AK4" s="12" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="AL4" s="12" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>Эталон / ориентир</t>
         </is>
       </c>
-      <c r="AM4" s="9" t="inlineStr">
+      <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>https://polytek.com/products/poly-75-80-liquid-rubber</t>
         </is>
       </c>
-      <c r="AN4" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AO4" s="9" t="inlineStr">
+      <c r="AN4" s="2" t="inlineStr">
         <is>
           <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5" ht="68.09999999999999" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>PU-CAST-004</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Полиуретан</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Быстротвердеющий литьевой эластомер</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Polytek</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>PT Flex 60</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="n">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Shore A</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>около 600 cP</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>около 5 мин</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>около 2 ч</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>235%</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>345 psi</t>
         </is>
       </c>
-      <c r="R5" s="9" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>70 pli, Die C</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="X5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Y5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Z5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AA5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AB5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AC5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AD5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AE5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AF5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AG5" s="9" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
         <is>
           <t>Быстрые опытные отливки</t>
         </is>
       </c>
-      <c r="AH5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AI5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AJ5" s="9" t="inlineStr">
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
         <is>
           <t>Не проводились</t>
         </is>
       </c>
-      <c r="AK5" s="12" t="inlineStr">
+      <c r="AK5" s="3" t="inlineStr">
         <is>
           <t>Низкий</t>
         </is>
       </c>
-      <c r="AL5" s="12" t="inlineStr">
+      <c r="AL5" s="3" t="inlineStr">
         <is>
           <t>Эталон / ориентир</t>
         </is>
       </c>
-      <c r="AM5" s="9" t="inlineStr">
+      <c r="AM5" s="2" t="inlineStr">
         <is>
           <t>https://polytek.com/products/pt-flex-60-liquid-rubber</t>
         </is>
       </c>
-      <c r="AN5" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AO5" s="9" t="inlineStr">
+      <c r="AN5" s="2" t="inlineStr">
         <is>
           <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6" ht="68.09999999999999" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>PU-CAST-005</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Полиуретан</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Быстротвердеющий литьевой эластомер</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Polytek</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>PT Flex 85</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Shore A</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>около 5 мин</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>около 2 ч</t>
         </is>
       </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>250%</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1064 psi</t>
         </is>
       </c>
-      <c r="R6" s="9" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>190 pli, Die C</t>
         </is>
       </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="X6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Y6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="Z6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AA6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AB6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AC6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AD6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AE6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AF6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AG6" s="9" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
         <is>
           <t>Очень жёсткие эластичные технические изделия; тонкостенные защитные детали</t>
         </is>
       </c>
-      <c r="AH6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AI6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AJ6" s="9" t="inlineStr">
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
         <is>
           <t>Не проводились</t>
         </is>
       </c>
-      <c r="AK6" s="12" t="inlineStr">
+      <c r="AK6" s="3" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="AL6" s="12" t="inlineStr">
+      <c r="AL6" s="3" t="inlineStr">
         <is>
           <t>Эталон / ориентир</t>
         </is>
       </c>
-      <c r="AM6" s="9" t="inlineStr">
+      <c r="AM6" s="5" t="inlineStr">
         <is>
           <t>https://polytek.com/products/pt-flex-85-liquid-rubber</t>
         </is>
       </c>
-      <c r="AN6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
-        </is>
-      </c>
-      <c r="AO6" s="9" t="inlineStr">
-        <is>
-          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="68.09999999999999" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Polytek</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Poly 75-90</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Tan / бежево-коричневый</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1.07 g/cc</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6000 cP</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2A:1B по массе</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10–15 мин</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>16 ч</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>774%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1979 psi</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>368 pli, Die C</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>Жёсткие резиноподобные технические детали; защитные элементы; контрольная точка Shore A90</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>Высокое заявленное удлинение; высокая прочность при растяжении; высокое сопротивление раздиру</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>https://polytek.com/products/poly-75-90-liquid-rubber</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="68.09999999999999" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Промышленный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Smooth-On</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>PMC-790</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Clear Amber</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1.07 g/cc</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3000 cP</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2A:1B по объёму и массе</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20 мин</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>48 ч</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>48 ч</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>550%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2000 psi</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>300 pli, Die C</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>&lt;0.001 in/in</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>Промышленные резиновые детали; ролики; ремни; ударо- и износостойкие технические изделия</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>Высокая заявленная прочность; сопротивление раздиру; ударостойкость и износостойкость</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>Рабочая температура требует отдельной проверки</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smooth-on.com/products/pmc-790/</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="inlineStr">
+        <is>
+          <t>Производитель рекомендует постотверждение 65 °C в течение 4–8 часов для повышения свойств. Не считать 65 °C заявленной максимальной рабочей температурой материала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="68.09999999999999" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Высокоэффективный гибкий литьевой полиуретан</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>RAMPF / Innovative Polymers</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>HP-2190</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3300 cP</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>100:30 pbw</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20–30 мин</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>3400 psi</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>Высоконагруженные гибкие и износостойкие технические детали</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>Высокая заявленная прочность при растяжении; производителем заявлена abrasion resistance</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>https://innovative-polymers.com/product/hp-2190-90a-high-performance-flexible-polyurethane/</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr">
+        <is>
+          <t>Карточка продукта обозначает материал как 90 Shore A; в общей таблице производителя указан диапазон 85–95A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="68.09999999999999" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Гибкий литьевой полиуретан</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>RAMPF / Innovative Polymers</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>IE-3290</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>975 cP</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38:100 pbw</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7–13 мин</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1750 psi</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>215 pli</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>Жёсткие гибкие технические изделия; резиноподобные защитные детали</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>https://innovative-polymers.com/product-group/casting-resins/</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="inlineStr">
+        <is>
+          <t>В общей технической таблице производителя указан диапазон твёрдости 80–90 Shore A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68.09999999999999" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Промышленный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Smooth-On</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PMC-770</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Light Amber</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1.04 g/cc</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3000 cP</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2A:1B по объёму и массе</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30 мин</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16 ч</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>16 ч</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>750%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>750 psi</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>200 pli, Die C</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>&lt;0.001 in/in</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки; колёса; шкивы; демпферы; вибро- и ударопоглощающие элементы; эластичные технические детали</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>Высокое заявленное удлинение; Shore A70; хорошая контрольная точка для более мягких резиноподобных деталей</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smooth-on.com/products/pmc-770/</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="inlineStr">
+        <is>
+          <t>Постотверждение при 65 °C в течение 4–8 часов может повышать физические свойства. Это не является заявленной рабочей температурой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68.09999999999999" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>НТЦ ТатХимПроект</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>POLILAST 60</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>60 ±5</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1.1 г/см³</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1:1 по массе</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20–40 мин</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>24 ч при 20±2 °C; 6 ч при 105±5 °C</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>не менее 500%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>не менее 6.0 МПа</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0.7–1.1%</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>−60 °C</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>+150 °C; кратковременно до +200 °C</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Заявлено производителем</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Заявлено производителем</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Бензопродукты — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>Озон и УФ — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>По данным производителя при правильной технологии обычно не требуется</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>Возможно</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>Более мягкие эластичные защитные детали; демпферы; кожухи; контрольная точка Shore A60</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>Стойкость к слабым кислотам и щёлочам, озону и УФ — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>https://tathimproekt.ru/katalog-produkczii/litevoj-poliuretan-polilast/polilast-60</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="inlineStr">
+        <is>
+          <t>Производитель рекомендует использовать разделительную смазку POLILAST S при работе с формами. Адгезив POLILAST 41 предназначен для повышения адгезии и не является разделительным составом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68.09999999999999" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>НТЦ ТатХимПроект</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>POLILAST 80</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>80 ±5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1.1 г/см³</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1:1 по массе</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20–40 мин</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>24 ч при 20±2 °C; 6 ч при 105±5 °C</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>не менее 400%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>не менее 15.0 МПа</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0.7–1.1%</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>−60 °C</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>+150 °C; кратковременно до +200 °C</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Заявлено производителем</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Заявлено производителем</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Бензопродукты — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>Озон и УФ — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>По данным производителя при правильной технологии обычно не требуется</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>Возможно</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>Жёсткие резиноподобные защитные кожухи; накладки; технические детали; первый кандидат проекта для физического испытания</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>Стойкость к слабым кислотам и щёлочам, озону и УФ — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Приоритетный кандидат</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
+        <is>
+          <t>https://tathimproekt.ru/katalog-produkczii/litevoj-poliuretan-polilast/polilast-80</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="inlineStr">
+        <is>
+          <t>Планируется как один из первых материалов для реальной пробной заливки.
+Производитель рекомендует использовать разделительную смазку POLILAST S при работе с формами. Адгезив POLILAST 41 предназначен для повышения адгезии и не является разделительным составом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="68.09999999999999" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>НТЦ ТатХимПроект</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>POLILAST 90</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>90 ±5</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1.1 г/см³</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1:1 по массе</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20–40 мин</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>24 ч при 20±2 °C</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>Очень жёсткие резиноподобные технические детали; контрольная точка Shore A90</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>https://tathimproekt.ru/katalog-produkczii/litevoj-poliuretan-polilast/polilast-90</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
+          <t>Производитель рекомендует использовать разделительную смазку POLILAST S при работе с формами. Адгезив POLILAST 41 предназначен для повышения адгезии и не является разделительным составом.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AK2:AK6">
-    <cfRule type="expression" priority="1" dxfId="0">
+  <conditionalFormatting sqref="AK2:AK14">
+    <cfRule type="expression" priority="1" dxfId="9">
       <formula>$AK2="Высокий"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="8">
       <formula>$AK2="Средний"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="7">
       <formula>$AK2="Низкий"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="6">
       <formula>$AK2="Не определён"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL6">
-    <cfRule type="expression" priority="5" dxfId="4">
+  <conditionalFormatting sqref="AL2:AL14">
+    <cfRule type="expression" priority="5" dxfId="5">
       <formula>$AL2="Приоритетный кандидат"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="4">
       <formula>$AL2="Куплен"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="3">
       <formula>$AL2="Испытывается"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>$AL2="Проверен"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
+    <cfRule type="expression" priority="9" dxfId="1">
       <formula>$AL2="Подходит"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9">
+    <cfRule type="expression" priority="10" dxfId="0">
       <formula>$AL2="Не подходит"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="AK2:AK6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AK2:AK6 AK7:AK11 AK12:AK14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Высокий,Средний,Низкий,Не определён"</formula1>
     </dataValidation>
-    <dataValidation sqref="AL2:AL6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AL2:AL6 AL7:AL11 AL12:AL14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Эталон / ориентир,Кандидат,Приоритетный кандидат,Куплен,Испытывается,Проверен,Подходит,Не подходит,ТРЕБУЕТ УТОЧНЕНИЯ"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Support/Материалы.xlsx
+++ b/Support/Материалы.xlsx
@@ -275,8 +275,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaterialsTable" displayName="MaterialsTable" ref="A1:AN14" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:AN14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaterialsTable" displayName="MaterialsTable" ref="A1:AN18" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:AN18"/>
   <tableColumns count="40">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Категория"/>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3370,8 +3370,817 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="68.09999999999999" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Технология-Пласт</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Силагерм 6080</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>80–85</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ / базовый цвет производителя</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>около 10 мин</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>около 8 ч</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>не менее 350%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>10–15 МПа</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>−50 °C — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>+70 °C — заявлено производителем</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>Возможно специальным совместимым красителем для полиуретанов</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>1,5 кг</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>Износостойкие и резиноподобные технические детали; защитные кожухи; накладки; экспериментальный аналог POLILAST 80</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Приоритетный кандидат</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>https://silagerm.com/products/25843378
+Ozon — комплект Силагерм 6080 1,5 кг: https://www.ozon.ru/product/poliuretan-dlya-izdeliy-i-form-silagerm-6080-komplekt-1-5-kg-925340653/</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
+        <is>
+          <t>Доступен в небольшой фасовке и рассматривается как один из наиболее удобных материалов для первой реальной покупки и испытаний. Для проекта требуется чёрный цвет. Готовый чёрный вариант в рассматриваемом предложении не подтверждён. Требуется отдельный совместимый чёрный PU-пигмент. Наличие подходящего чёрного красителя на Ozon не считать подтверждённым. Не использовать водные и случайные универсальные строительные колеры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="68.09999999999999" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Lastor</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Lastor 7780</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>80 ±2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1.08 г/см³</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>более 290%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>16.8 МПа</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>Допускается фирменной пигментной пастой Lastor для полиуретанов</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>2 кг</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>Жёсткие резиноподобные технические изделия; прямой кандидат для сравнения с POLILAST 80 и Силагерм 6080</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>https://lastor.ru/product/poliuretanovyj-kompaund-lastor-7780/</t>
+        </is>
+      </c>
+      <c r="AN16" s="2" t="inlineStr">
+        <is>
+          <t>Для проекта нужен чёрный цвет. У Lastor существует фирменная чёрная пигментная паста для полиуретанов. Точную рекомендуемую дозировку именно для Lastor 7780 перед использованием уточнить у производителя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="68.09999999999999" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Технология-Пласт</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Силагерм 6090</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>около 90</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>Более жёсткая контрольная точка для сравнения материалов около Shore A90</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr">
+        <is>
+          <t>Для чёрного цвета требуется совместимый PU-краситель; совместимость с Силагерм 6090 уточнить. Наличие подходящего чёрного красителя на Ozon не подтверждено и не должно считаться подтверждённым.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="68.09999999999999" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PU-CAST-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Полиуретан</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомпонентный литьевой эластомер</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Lastor</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Lastor 7790</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>90 ±2</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Shore A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>более 247%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>около 27 МПа</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>Допускается фирменной пигментной пастой Lastor для полиуретанов</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>2 кг</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>Очень жёсткие резиноподобные изделия; контрольный кандидат Shore A90</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>Не проводились</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Кандидат</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>ТРЕБУЕТ УТОЧНЕНИЯ</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>Для чёрного изделия предполагается окрашивание совместимой чёрной PU-пигментной пастой. Фирменная пигментная паста Lastor для полиуретанов существует; дозировку для данного материала уточнить.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="AK2:AK14">
+  <conditionalFormatting sqref="AK2:AK18">
     <cfRule type="expression" priority="1" dxfId="9">
       <formula>$AK2="Высокий"</formula>
     </cfRule>
@@ -3385,7 +4194,7 @@
       <formula>$AK2="Не определён"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL14">
+  <conditionalFormatting sqref="AL2:AL18">
     <cfRule type="expression" priority="5" dxfId="5">
       <formula>$AL2="Приоритетный кандидат"</formula>
     </cfRule>
@@ -3406,10 +4215,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="AK2:AK6 AK7:AK11 AK12:AK14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AK2:AK6 AK7:AK11 AK12:AK14 AK15:AK18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Высокий,Средний,Низкий,Не определён"</formula1>
     </dataValidation>
-    <dataValidation sqref="AL2:AL6 AL7:AL11 AL12:AL14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AL2:AL6 AL7:AL11 AL12:AL14 AL15:AL18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Эталон / ориентир,Кандидат,Приоритетный кандидат,Куплен,Испытывается,Проверен,Подходит,Не подходит,ТРЕБУЕТ УТОЧНЕНИЯ"</formula1>
     </dataValidation>
   </dataValidations>
